--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548748.4147140213</v>
+        <v>548748</v>
       </c>
       <c r="R2" t="n">
-        <v>6352929.76600089</v>
+        <v>6352930</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548748.4147140213</v>
+        <v>548748</v>
       </c>
       <c r="R3" t="n">
-        <v>6352929.76600089</v>
+        <v>6352930</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +850,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -926,12 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548748.4147140213</v>
+        <v>548748</v>
       </c>
       <c r="R4" t="n">
-        <v>6352929.76600089</v>
+        <v>6352930</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,19 +961,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4574-2021 artfynd.xlsx
+++ b/artfynd/A 4574-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153388</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74604313</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74766926</v>
       </c>
       <c r="B4" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
